--- a/forecast_app_final/data/Summary.xlsx
+++ b/forecast_app_final/data/Summary.xlsx
@@ -417,13 +417,13 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>720</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>2</v>
@@ -437,13 +437,13 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>752</v>
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>125</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -457,13 +457,13 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>789</v>
+        <v>39</v>
       </c>
       <c r="C4">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>66</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -477,13 +477,13 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>769</v>
+        <v>67</v>
       </c>
       <c r="C5">
-        <v>128</v>
+        <v>11</v>
       </c>
       <c r="D5">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -497,13 +497,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>628</v>
+        <v>83</v>
       </c>
       <c r="C6">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="E6">
         <v>2</v>
@@ -517,13 +517,13 @@
         <v>11</v>
       </c>
       <c r="B7">
-        <v>662</v>
+        <v>130</v>
       </c>
       <c r="C7">
-        <v>110</v>
+        <v>22</v>
       </c>
       <c r="D7">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -537,13 +537,13 @@
         <v>12</v>
       </c>
       <c r="B8">
-        <v>676</v>
+        <v>143</v>
       </c>
       <c r="C8">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="D8">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="E8">
         <v>4</v>
@@ -557,13 +557,13 @@
         <v>13</v>
       </c>
       <c r="B9">
-        <v>591</v>
+        <v>109</v>
       </c>
       <c r="C9">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="E9">
         <v>4</v>
@@ -577,13 +577,13 @@
         <v>14</v>
       </c>
       <c r="B10">
-        <v>616</v>
+        <v>236</v>
       </c>
       <c r="C10">
-        <v>103</v>
+        <v>39</v>
       </c>
       <c r="D10">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -597,13 +597,13 @@
         <v>15</v>
       </c>
       <c r="B11">
-        <v>609</v>
+        <v>206</v>
       </c>
       <c r="C11">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D11">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>4</v>
@@ -617,13 +617,13 @@
         <v>16</v>
       </c>
       <c r="B12">
-        <v>524</v>
+        <v>221</v>
       </c>
       <c r="C12">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="D12">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="E12">
         <v>4</v>
@@ -637,13 +637,13 @@
         <v>17</v>
       </c>
       <c r="B13">
-        <v>448</v>
+        <v>183</v>
       </c>
       <c r="C13">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E13">
         <v>4</v>
@@ -657,13 +657,13 @@
         <v>18</v>
       </c>
       <c r="B14">
-        <v>373</v>
+        <v>191</v>
       </c>
       <c r="C14">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="E14">
         <v>4</v>
@@ -677,13 +677,13 @@
         <v>19</v>
       </c>
       <c r="B15">
-        <v>253</v>
+        <v>206</v>
       </c>
       <c r="C15">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D15">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <v>4</v>
@@ -697,13 +697,13 @@
         <v>20</v>
       </c>
       <c r="B16">
-        <v>242</v>
+        <v>200</v>
       </c>
       <c r="C16">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D16">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E16">
         <v>4</v>
@@ -717,13 +717,13 @@
         <v>21</v>
       </c>
       <c r="B17">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="C17">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -737,13 +737,13 @@
         <v>22</v>
       </c>
       <c r="B18">
-        <v>318</v>
+        <v>172</v>
       </c>
       <c r="C18">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="D18">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>4</v>
@@ -757,13 +757,13 @@
         <v>23</v>
       </c>
       <c r="B19">
-        <v>360</v>
+        <v>157</v>
       </c>
       <c r="C19">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -777,13 +777,13 @@
         <v>0</v>
       </c>
       <c r="B20">
-        <v>494</v>
+        <v>117</v>
       </c>
       <c r="C20">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E20">
         <v>3</v>
@@ -797,13 +797,13 @@
         <v>1</v>
       </c>
       <c r="B21">
-        <v>611</v>
+        <v>98</v>
       </c>
       <c r="C21">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="D21">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E21">
         <v>3</v>
@@ -817,13 +817,13 @@
         <v>2</v>
       </c>
       <c r="B22">
-        <v>631</v>
+        <v>56</v>
       </c>
       <c r="C22">
-        <v>105</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="E22">
         <v>2</v>
@@ -837,13 +837,13 @@
         <v>3</v>
       </c>
       <c r="B23">
-        <v>746</v>
+        <v>49</v>
       </c>
       <c r="C23">
-        <v>124</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="E23">
         <v>2</v>
@@ -857,13 +857,13 @@
         <v>4</v>
       </c>
       <c r="B24">
-        <v>800</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E24">
         <v>2</v>
@@ -877,13 +877,13 @@
         <v>5</v>
       </c>
       <c r="B25">
-        <v>702</v>
+        <v>9</v>
       </c>
       <c r="C25">
-        <v>117</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="E25">
         <v>1</v>
